--- a/DateBase/orders/Nha Thu_2026-3-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-22.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,10 +606,317 @@
       <c r="C21" t="str">
         <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>5</v>
+      </c>
+      <c r="C24" t="str">
+        <v>320_雪柳花_Spiraea flower white_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>864_黄洋金边红色_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>129_绣球初恋_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F27" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6</v>
+      </c>
+      <c r="C34" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>533_风车果_scabiosa pods_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>7</v>
+      </c>
+      <c r="C39" t="str">
+        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F41" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>607_康乃馨芙蓉_light orange_undefined_20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>8</v>
+      </c>
+      <c r="C47" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>1</v>
+      </c>
+      <c r="C48" t="str">
+        <v>834_海芋黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2</v>
+      </c>
+      <c r="C49" t="str">
+        <v>843_灯台_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>483_圣诞花_mimosa_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>3</v>
+      </c>
+      <c r="C53" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>4</v>
+      </c>
+      <c r="C54" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>42_拉丝黄_Spider Yellow_Gerbera L._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L56"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +971,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>07540115871551088108205101351050</v>
+        <v>07540115871551088108205101351055810151010157291010310101510107101551053010345101513301055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-22.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-22.xlsx
@@ -973,6 +973,9 @@
       <c r="G2" t="str">
         <v>07540115871551088108205101351055810151010157291010310101510107101551053010345101513301055</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
